--- a/Packages/cn.etetet.yiuilubangen/Luban/Config/Datas/Puzzle.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Luban/Config/Datas/Puzzle.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="12780"/>
+    <workbookView windowWidth="22296" windowHeight="13908"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="23">
   <si>
     <t>##var</t>
   </si>
@@ -38,12 +38,6 @@
     <t>Name</t>
   </si>
   <si>
-    <t>X</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>PrefabPath</t>
   </si>
   <si>
@@ -71,12 +65,6 @@
     <t>名字</t>
   </si>
   <si>
-    <t>x</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
     <t>预制体路径</t>
   </si>
   <si>
@@ -99,6 +87,15 @@
   </si>
   <si>
     <t>0,0;1,0;-1,0</t>
+  </si>
+  <si>
+    <t>6格拼图</t>
+  </si>
+  <si>
+    <t>Puzzle/Puzzle1003</t>
+  </si>
+  <si>
+    <t>0,0;0,-1;1,0;0,1;1,-1;1,1</t>
   </si>
 </sst>
 </file>
@@ -111,7 +108,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -131,13 +128,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <u/>
@@ -593,148 +583,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1069,14 +1059,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="6"/>
+  <dimension ref="A1:E8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" outlineLevelRow="7" outlineLevelCol="4"/>
   <cols>
-    <col min="6" max="6" width="17.7777777777778" customWidth="1"/>
-    <col min="7" max="7" width="35.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="17.7777777777778" customWidth="1"/>
+    <col min="5" max="5" width="35.6666666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1092,125 +1082,97 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="D2" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" t="s">
         <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>11</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>17</v>
-      </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="1:5">
       <c r="B5" s="2">
         <v>1001</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="2">
-        <v>1</v>
-      </c>
-      <c r="E5" s="2">
-        <v>1</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
+        <v>14</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="1:5">
       <c r="B6" s="2">
         <v>1002</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="2">
-        <v>1</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="E7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
     </row>
-    <row r="7" spans="2:7">
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="1:5">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="D8" s="4"/>
       <c r="E8" s="2"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
